--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Clone\23-kcvn-spm-be\src\main\kotlin\com\kcvn\spm\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KCVN\23-kcvn-spm-be\src\main\kotlin\com\kcvn\spm\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -59,9 +59,6 @@
     <t>Ngày - giờ bắt đầu</t>
   </si>
   <si>
-    <t>Ngày giờ kết thúc</t>
-  </si>
-  <si>
     <t>Số đơn đặt hàng chế tạo</t>
   </si>
   <si>
@@ -86,21 +83,9 @@
     <t>Số chiếc</t>
   </si>
   <si>
-    <t>Số tấm sp xử lý</t>
-  </si>
-  <si>
-    <t>Số tấm sheer xử lý</t>
-  </si>
-  <si>
     <t>SL sản phẩm tốt</t>
   </si>
   <si>
-    <t>Số tấm sản phẩm tốt</t>
-  </si>
-  <si>
-    <t>Số tấm sheer tốt</t>
-  </si>
-  <si>
     <t>Rest</t>
   </si>
   <si>
@@ -111,6 +96,21 @@
   </si>
   <si>
     <t>Đội</t>
+  </si>
+  <si>
+    <t>Ngày - giờ kết thúc</t>
+  </si>
+  <si>
+    <t>Số sản phẩm xử lý</t>
+  </si>
+  <si>
+    <t>Số sheet xử lý</t>
+  </si>
+  <si>
+    <t>Số sản phẩm tốt</t>
+  </si>
+  <si>
+    <t>Số sheet tốt</t>
   </si>
 </sst>
 </file>
@@ -201,7 +201,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -399,7 +399,35 @@
   <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="32.7109375" style="1"/>
+    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="20.140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="21" style="1" customWidth="1"/>
+    <col min="21" max="21" width="22.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="20.85546875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="18" style="1" customWidth="1"/>
+    <col min="24" max="24" width="19" style="1" customWidth="1"/>
+    <col min="25" max="25" width="23.140625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="23.42578125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="21.85546875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="41.7109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="32.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="32.25" customHeight="1">
@@ -434,12 +462,12 @@
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
     </row>
-    <row r="2" spans="1:28" s="4" customFormat="1">
+    <row r="2" spans="1:28" s="4" customFormat="1" ht="37.5" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>7</v>
@@ -457,58 +485,58 @@
         <v>10</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="U2" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z2" s="4" t="s">
         <v>4</v>
@@ -517,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -189,10 +189,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,8 +200,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -399,35 +402,35 @@
   <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="20.140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="21" style="1" customWidth="1"/>
-    <col min="21" max="21" width="22.140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="20.85546875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="18" style="1" customWidth="1"/>
-    <col min="24" max="24" width="19" style="1" customWidth="1"/>
-    <col min="25" max="25" width="23.140625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="23.42578125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="21.85546875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="41.7109375" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="32.7109375" style="1"/>
+    <col min="1" max="1" width="16.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="30" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="23.85546875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="19" style="4" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="4" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="20.140625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="21" style="5" customWidth="1"/>
+    <col min="21" max="21" width="22.140625" style="5" customWidth="1"/>
+    <col min="22" max="22" width="20.85546875" style="5" customWidth="1"/>
+    <col min="23" max="23" width="18" style="4" customWidth="1"/>
+    <col min="24" max="24" width="19" style="4" customWidth="1"/>
+    <col min="25" max="25" width="23.140625" style="4" customWidth="1"/>
+    <col min="26" max="26" width="23.42578125" style="4" customWidth="1"/>
+    <col min="27" max="27" width="41.28515625" style="4" customWidth="1"/>
+    <col min="28" max="28" width="41.7109375" style="4" customWidth="1"/>
+    <col min="29" max="16384" width="32.7109375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="32.25" customHeight="1">
@@ -462,89 +465,89 @@
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
     </row>
-    <row r="2" spans="1:28" s="4" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:28" s="1" customFormat="1" ht="37.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AA2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AB2" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -189,9 +189,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -199,12 +202,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -402,68 +399,68 @@
   <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="30" style="4" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="19" style="4" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="4" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" style="5" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="20.140625" style="5" customWidth="1"/>
-    <col min="20" max="20" width="21" style="5" customWidth="1"/>
-    <col min="21" max="21" width="22.140625" style="5" customWidth="1"/>
-    <col min="22" max="22" width="20.85546875" style="5" customWidth="1"/>
-    <col min="23" max="23" width="18" style="4" customWidth="1"/>
-    <col min="24" max="24" width="19" style="4" customWidth="1"/>
-    <col min="25" max="25" width="23.140625" style="4" customWidth="1"/>
-    <col min="26" max="26" width="23.42578125" style="4" customWidth="1"/>
-    <col min="27" max="27" width="41.28515625" style="4" customWidth="1"/>
-    <col min="28" max="28" width="41.7109375" style="4" customWidth="1"/>
-    <col min="29" max="16384" width="32.7109375" style="4"/>
+    <col min="1" max="1" width="16.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.85546875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19" style="2" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="20.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="21" style="2" customWidth="1"/>
+    <col min="21" max="21" width="22.140625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="20.85546875" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18" style="2" customWidth="1"/>
+    <col min="24" max="24" width="19" style="2" customWidth="1"/>
+    <col min="25" max="25" width="23.140625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="23.42578125" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.28515625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="41.7109375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="32.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="32.25" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
     </row>
     <row r="2" spans="1:28" s="1" customFormat="1" ht="37.5" customHeight="1">
       <c r="A2" s="1" t="s">

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Kết quả sản xuất" sheetId="1" r:id="rId1"/>
+    <sheet name="Kết qủa sản xuất" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -117,17 +117,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -189,18 +183,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -397,72 +388,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="19" style="2" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="20.140625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="21" style="2" customWidth="1"/>
-    <col min="21" max="21" width="22.140625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="20.85546875" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18" style="2" customWidth="1"/>
-    <col min="24" max="24" width="19" style="2" customWidth="1"/>
-    <col min="25" max="25" width="23.140625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="23.42578125" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.28515625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="41.7109375" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="32.7109375" style="2"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="27.5703125" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" customWidth="1"/>
+    <col min="18" max="18" width="18.5703125" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" customWidth="1"/>
+    <col min="20" max="20" width="16.28515625" customWidth="1"/>
+    <col min="21" max="21" width="18.5703125" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" customWidth="1"/>
+    <col min="24" max="24" width="15.85546875" customWidth="1"/>
+    <col min="25" max="26" width="21.7109375" customWidth="1"/>
+    <col min="27" max="28" width="39.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.25" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:28" ht="31.5" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
     </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" ht="37.5" customHeight="1">
+    <row r="2" spans="1:28" ht="36.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -552,7 +539,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -101,16 +101,19 @@
     <t>Ngày - giờ kết thúc</t>
   </si>
   <si>
-    <t>Số sản phẩm xử lý</t>
-  </si>
-  <si>
-    <t>Số sheet xử lý</t>
-  </si>
-  <si>
-    <t>Số sản phẩm tốt</t>
-  </si>
-  <si>
-    <t>Số sheet tốt</t>
+    <t>Số tấm 
+sản phẩm tốt</t>
+  </si>
+  <si>
+    <t>Số tấm 
+sản phẩm xử lý</t>
+  </si>
+  <si>
+    <t>Số tấm 
+sheer xử lý</t>
+  </si>
+  <si>
+    <t>Số tấm sheer tốt</t>
   </si>
 </sst>
 </file>
@@ -407,7 +410,7 @@
     <col min="15" max="15" width="17.42578125" customWidth="1"/>
     <col min="17" max="17" width="16.140625" customWidth="1"/>
     <col min="18" max="18" width="18.5703125" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" customWidth="1"/>
+    <col min="19" max="19" width="15.85546875" customWidth="1"/>
     <col min="20" max="20" width="16.28515625" customWidth="1"/>
     <col min="21" max="21" width="18.5703125" customWidth="1"/>
     <col min="22" max="22" width="17.42578125" customWidth="1"/>
@@ -502,16 +505,16 @@
         <v>18</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>28</v>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Kết qủa sản xuất" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kết qủa sản xuất'!$A$2:$AB$2</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -539,6 +542,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:AB2"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
   </mergeCells>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportWorkResultTemplate.xlsx
@@ -135,14 +135,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -165,21 +164,32 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -189,15 +199,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -396,64 +409,66 @@
   <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
-    <col min="8" max="8" width="27.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="20.28515625" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="17" max="17" width="16.140625" customWidth="1"/>
-    <col min="18" max="18" width="18.5703125" customWidth="1"/>
-    <col min="19" max="19" width="15.85546875" customWidth="1"/>
-    <col min="20" max="20" width="16.28515625" customWidth="1"/>
-    <col min="21" max="21" width="18.5703125" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" customWidth="1"/>
-    <col min="24" max="24" width="15.85546875" customWidth="1"/>
-    <col min="25" max="26" width="21.7109375" customWidth="1"/>
-    <col min="27" max="28" width="39.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="2"/>
+    <col min="17" max="17" width="16.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="18.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="15.85546875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="16.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.5703125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="15.85546875" style="2" customWidth="1"/>
+    <col min="25" max="26" width="21.7109375" style="2" customWidth="1"/>
+    <col min="27" max="28" width="39.85546875" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="31.5" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
     </row>
     <row r="2" spans="1:28" ht="36.75" customHeight="1">
       <c r="A2" s="1" t="s">
